--- a/output/pdf_financials_xlsx/BKMT.xlsx
+++ b/output/pdf_financials_xlsx/BKMT.xlsx
@@ -3681,22 +3681,22 @@
         <v>0.006485</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.013495</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.013495</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.013495</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.013495</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.143639</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.134667</v>
       </c>
     </row>
     <row r="92">
@@ -3706,31 +3706,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.6082920000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.0303</v>
+        <v>0.0478</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.0303</v>
+        <v>0.0478</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.4029</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.4029</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.3854</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.3854</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.3854</v>
       </c>
     </row>
     <row r="93">
@@ -5751,7 +5751,11 @@
           <t>Share-based payment reserve (note 7)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5806,7 +5810,11 @@
           <t>Digital currency revaluation reserve (note 5)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -5861,7 +5869,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -6224,7 +6236,11 @@
           <t>Share-based payment reserve (note 8)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -6279,7 +6295,11 @@
           <t>Digital currency revaluation reserve (note 6)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -6448,7 +6468,11 @@
           <t>Share-based payment reserve (note 10)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -6501,7 +6525,11 @@
           <t>Warrant reserve (note 11)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -7343,7 +7371,11 @@
           <t>Share-based payment reserve (note 11)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -7398,7 +7430,11 @@
           <t>Warrant reserve (note 12)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -8569,7 +8605,11 @@
           <t>Share-based payment reserve total</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.6082920000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/BKMT.xlsx
+++ b/output/pdf_financials_xlsx/BKMT.xlsx
@@ -1670,31 +1670,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.6082920000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.232402</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.957158</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.600962</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.032371</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.636966</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.532827</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.324003</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.161339</v>
       </c>
     </row>
     <row r="35">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.6082920000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.232402</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.957158</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.600962</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.032371</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.636966</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.532827</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.324003</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.161339</v>
       </c>
     </row>
     <row r="37">
@@ -2149,19 +2149,19 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.285454</v>
+        <v>0.053052</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.958691</v>
+        <v>0.001533</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.601962</v>
+        <v>0.001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.07607</v>
+        <v>0.043699</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.74146</v>
+        <v>0.104494</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
@@ -16726,7 +16726,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">

--- a/output/pdf_financials_xlsx/BKMT.xlsx
+++ b/output/pdf_financials_xlsx/BKMT.xlsx
@@ -1142,14 +1142,20 @@
       <c r="E20" s="3" t="n">
         <v>-0.425833</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-1.122942</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>-0.543279</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0.116725</v>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.157234</v>
@@ -1179,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.003431</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-0.543279</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>0.116725</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -4330,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.15356</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -4339,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.537654</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -4463,7 +4469,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.019875</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -5146,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.15356</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -5155,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.537654</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -5180,7 +5186,7 @@
         <v>-0.035338</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.693492</v>
+        <v>-1.847052</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.689948</v>
@@ -5189,7 +5195,7 @@
         <v>-0.363206</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.800085</v>
+        <v>-1.337739</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.289684</v>
@@ -10993,7 +10999,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -12367,7 +12377,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -13231,7 +13245,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
         <v>0.6</v>
       </c>
@@ -13416,7 +13434,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E137" s="5" t="n">
         <v>0.019875</v>
       </c>
@@ -15054,7 +15076,11 @@
           <t>Net income from discontinued operations (note 5)</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -15809,7 +15835,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -15988,7 +16014,11 @@
           <t>Net loss from discontinued operations (note 5)</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
